--- a/chapter4_tables.xlsx
+++ b/chapter4_tables.xlsx
@@ -1044,7 +1044,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>PM2.5 exposure</t>
+          <t>Anthropogenic PM2.5 exposure</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>C32 PM2.5 exposure</t>
+          <t>C32 Anthropogenic PM2.5 exposure</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
